--- a/school_1/school_1_KP.xlsx
+++ b/school_1/school_1_KP.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425"/>
   </bookViews>
@@ -2769,6 +2774,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2799,40 +2837,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3145,10 +3150,11 @@
   <dimension ref="A1:AI223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="55.5703125" customWidth="1"/>
-    <col min="4" max="5" width="38" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" customWidth="1"/>
     <col min="6" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" customWidth="1"/>
@@ -3226,79 +3232,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
@@ -3328,115 +3334,115 @@
       <c r="I5" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="36" t="s">
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="36" t="s">
+      <c r="Q5" s="48"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="37"/>
-      <c r="U5" s="38"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="49"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="42" t="s">
+      <c r="A6" s="50"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="43"/>
+      <c r="K6" s="32"/>
       <c r="L6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="43"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="43"/>
+      <c r="Q6" s="32"/>
       <c r="R6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="S6" s="42" t="s">
+      <c r="S6" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="43"/>
+      <c r="T6" s="32"/>
       <c r="U6" s="39" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
       <c r="J7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="41"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="41"/>
+      <c r="O7" s="40"/>
       <c r="P7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="41"/>
+      <c r="R7" s="40"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="41"/>
+      <c r="U7" s="40"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="46"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -3490,15 +3496,15 @@
       <c r="B9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="49"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="35"/>
       <c r="M9" s="6">
         <f>SUM(M10,M20)</f>
         <v>7389478.8500000006</v>
@@ -3549,15 +3555,15 @@
       <c r="B10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="49"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="35"/>
       <c r="M10" s="6">
         <f t="shared" ref="M10:O14" si="0">SUM(M11)</f>
         <v>281586.05</v>
@@ -3608,15 +3614,15 @@
       <c r="B11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="49"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="35"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>281586.05</v>
@@ -3667,15 +3673,15 @@
       <c r="B12" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="35"/>
       <c r="M12" s="6">
         <f t="shared" si="0"/>
         <v>281586.05</v>
@@ -3726,15 +3732,15 @@
       <c r="B13" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="49"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="35"/>
       <c r="M13" s="6">
         <f t="shared" si="0"/>
         <v>281586.05</v>
@@ -3785,15 +3791,15 @@
       <c r="B14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="49"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="35"/>
       <c r="M14" s="6">
         <f t="shared" si="0"/>
         <v>281586.05</v>
@@ -4164,15 +4170,15 @@
       <c r="B20" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="49"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="35"/>
       <c r="M20" s="6">
         <f t="shared" ref="M20:O21" si="3">SUM(M21)</f>
         <v>7107892.8000000007</v>
@@ -4223,15 +4229,15 @@
       <c r="B21" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="49"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="35"/>
       <c r="M21" s="6">
         <f t="shared" si="3"/>
         <v>7107892.8000000007</v>
@@ -4282,15 +4288,15 @@
       <c r="B22" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="49"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="35"/>
       <c r="M22" s="6">
         <f>SUM(M23,M92,M171,M201)</f>
         <v>7107892.8000000007</v>
@@ -4341,15 +4347,15 @@
       <c r="B23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="49"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="35"/>
       <c r="M23" s="6">
         <f>SUM(M24,M50,M59)</f>
         <v>6027366.1100000003</v>
@@ -4400,15 +4406,15 @@
       <c r="B24" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="49"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="35"/>
       <c r="M24" s="6">
         <f>SUM(M25,M28,M30,M32,M37,M41,M46)</f>
         <v>1198182.1600000001</v>
@@ -6177,15 +6183,15 @@
       <c r="B50" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="49"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="35"/>
       <c r="M50" s="6">
         <f>SUM(M51,M54,M57)</f>
         <v>2801904.2</v>
@@ -6828,15 +6834,15 @@
       <c r="B59" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="C59" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="49"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="35"/>
       <c r="M59" s="6">
         <f>SUM(M60,M65,M70,M75,M79,M82,M87)</f>
         <v>2027279.7499999998</v>
@@ -6880,7 +6886,7 @@
         <v>16075337</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>252</v>
       </c>
@@ -7202,7 +7208,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>280</v>
       </c>
@@ -7468,7 +7474,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>291</v>
       </c>
@@ -7522,7 +7528,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>297</v>
       </c>
@@ -8008,7 +8014,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>326</v>
       </c>
@@ -8973,15 +8979,15 @@
       <c r="B92" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C92" s="47" t="s">
+      <c r="C92" s="33" t="s">
         <v>394</v>
       </c>
-      <c r="D92" s="48"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="49"/>
+      <c r="D92" s="34"/>
+      <c r="E92" s="34"/>
+      <c r="F92" s="34"/>
+      <c r="G92" s="34"/>
+      <c r="H92" s="34"/>
+      <c r="I92" s="35"/>
       <c r="M92" s="6">
         <f>SUM(M93,M167)</f>
         <v>627271.60000000021</v>
@@ -9032,15 +9038,15 @@
       <c r="B93" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="C93" s="47" t="s">
+      <c r="C93" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="D93" s="48"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="49"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="34"/>
+      <c r="F93" s="34"/>
+      <c r="G93" s="34"/>
+      <c r="H93" s="34"/>
+      <c r="I93" s="35"/>
       <c r="M93" s="6">
         <f>SUM(M94,M99,M104,M108,M112,M117,M122,M126,M130,M134,M138,M143,M148,M152,M157,M162)</f>
         <v>613448.95000000019</v>
@@ -9834,7 +9840,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>441</v>
       </c>
@@ -10206,7 +10212,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>462</v>
       </c>
@@ -12232,7 +12238,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
         <v>563</v>
       </c>
@@ -13829,15 +13835,15 @@
       <c r="B167" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="C167" s="47" t="s">
+      <c r="C167" s="33" t="s">
         <v>633</v>
       </c>
-      <c r="D167" s="48"/>
-      <c r="E167" s="48"/>
-      <c r="F167" s="48"/>
-      <c r="G167" s="48"/>
-      <c r="H167" s="48"/>
-      <c r="I167" s="49"/>
+      <c r="D167" s="34"/>
+      <c r="E167" s="34"/>
+      <c r="F167" s="34"/>
+      <c r="G167" s="34"/>
+      <c r="H167" s="34"/>
+      <c r="I167" s="35"/>
       <c r="M167" s="6">
         <f>SUM(M168)</f>
         <v>13822.65</v>
@@ -14104,15 +14110,15 @@
       <c r="B171" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="C171" s="47" t="s">
+      <c r="C171" s="33" t="s">
         <v>651</v>
       </c>
-      <c r="D171" s="48"/>
-      <c r="E171" s="48"/>
-      <c r="F171" s="48"/>
-      <c r="G171" s="48"/>
-      <c r="H171" s="48"/>
-      <c r="I171" s="49"/>
+      <c r="D171" s="34"/>
+      <c r="E171" s="34"/>
+      <c r="F171" s="34"/>
+      <c r="G171" s="34"/>
+      <c r="H171" s="34"/>
+      <c r="I171" s="35"/>
       <c r="M171" s="6">
         <f>SUM(M172,M194)</f>
         <v>453255.09000000008</v>
@@ -14163,15 +14169,15 @@
       <c r="B172" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="C172" s="47" t="s">
+      <c r="C172" s="33" t="s">
         <v>654</v>
       </c>
-      <c r="D172" s="48"/>
-      <c r="E172" s="48"/>
-      <c r="F172" s="48"/>
-      <c r="G172" s="48"/>
-      <c r="H172" s="48"/>
-      <c r="I172" s="49"/>
+      <c r="D172" s="34"/>
+      <c r="E172" s="34"/>
+      <c r="F172" s="34"/>
+      <c r="G172" s="34"/>
+      <c r="H172" s="34"/>
+      <c r="I172" s="35"/>
       <c r="M172" s="6">
         <f>SUM(M173,M176,M179,M182,M185,M188,M191)</f>
         <v>362095.37000000005</v>
@@ -15724,15 +15730,15 @@
       <c r="B194" s="10" t="s">
         <v>713</v>
       </c>
-      <c r="C194" s="47" t="s">
+      <c r="C194" s="33" t="s">
         <v>714</v>
       </c>
-      <c r="D194" s="48"/>
-      <c r="E194" s="48"/>
-      <c r="F194" s="48"/>
-      <c r="G194" s="48"/>
-      <c r="H194" s="48"/>
-      <c r="I194" s="49"/>
+      <c r="D194" s="34"/>
+      <c r="E194" s="34"/>
+      <c r="F194" s="34"/>
+      <c r="G194" s="34"/>
+      <c r="H194" s="34"/>
+      <c r="I194" s="35"/>
       <c r="M194" s="6">
         <f>SUM(M195,M198)</f>
         <v>91159.72</v>
@@ -16215,15 +16221,15 @@
       <c r="B201" s="10" t="s">
         <v>739</v>
       </c>
-      <c r="C201" s="47" t="s">
+      <c r="C201" s="33" t="s">
         <v>740</v>
       </c>
-      <c r="D201" s="48"/>
-      <c r="E201" s="48"/>
-      <c r="F201" s="48"/>
-      <c r="G201" s="48"/>
-      <c r="H201" s="48"/>
-      <c r="I201" s="49"/>
+      <c r="D201" s="34"/>
+      <c r="E201" s="34"/>
+      <c r="F201" s="34"/>
+      <c r="G201" s="34"/>
+      <c r="H201" s="34"/>
+      <c r="I201" s="35"/>
       <c r="M201" s="6">
         <f>SUM(M202)</f>
         <v>0</v>
@@ -16487,29 +16493,29 @@
       </c>
     </row>
     <row r="205" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A205" s="44" t="s">
+      <c r="A205" s="36" t="s">
         <v>754</v>
       </c>
-      <c r="B205" s="45"/>
-      <c r="C205" s="45"/>
-      <c r="D205" s="45"/>
-      <c r="E205" s="45"/>
-      <c r="F205" s="45"/>
-      <c r="G205" s="45"/>
-      <c r="H205" s="45"/>
-      <c r="I205" s="45"/>
-      <c r="J205" s="45"/>
-      <c r="K205" s="45"/>
-      <c r="L205" s="45"/>
-      <c r="M205" s="45"/>
-      <c r="N205" s="45"/>
-      <c r="O205" s="45"/>
-      <c r="P205" s="45"/>
-      <c r="Q205" s="45"/>
-      <c r="R205" s="45"/>
-      <c r="S205" s="45"/>
-      <c r="T205" s="45"/>
-      <c r="U205" s="46"/>
+      <c r="B205" s="37"/>
+      <c r="C205" s="37"/>
+      <c r="D205" s="37"/>
+      <c r="E205" s="37"/>
+      <c r="F205" s="37"/>
+      <c r="G205" s="37"/>
+      <c r="H205" s="37"/>
+      <c r="I205" s="37"/>
+      <c r="J205" s="37"/>
+      <c r="K205" s="37"/>
+      <c r="L205" s="37"/>
+      <c r="M205" s="37"/>
+      <c r="N205" s="37"/>
+      <c r="O205" s="37"/>
+      <c r="P205" s="37"/>
+      <c r="Q205" s="37"/>
+      <c r="R205" s="37"/>
+      <c r="S205" s="37"/>
+      <c r="T205" s="37"/>
+      <c r="U205" s="38"/>
     </row>
     <row r="206" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="28"/>
@@ -16525,20 +16531,20 @@
       <c r="E206" s="29"/>
       <c r="F206" s="29"/>
       <c r="G206" s="29"/>
-      <c r="H206" s="42"/>
-      <c r="I206" s="50"/>
-      <c r="J206" s="50"/>
-      <c r="K206" s="50"/>
-      <c r="L206" s="50"/>
-      <c r="M206" s="50"/>
-      <c r="N206" s="50"/>
-      <c r="O206" s="50"/>
-      <c r="P206" s="50"/>
-      <c r="Q206" s="50"/>
-      <c r="R206" s="50"/>
-      <c r="S206" s="50"/>
-      <c r="T206" s="50"/>
-      <c r="U206" s="43"/>
+      <c r="H206" s="30"/>
+      <c r="I206" s="31"/>
+      <c r="J206" s="31"/>
+      <c r="K206" s="31"/>
+      <c r="L206" s="31"/>
+      <c r="M206" s="31"/>
+      <c r="N206" s="31"/>
+      <c r="O206" s="31"/>
+      <c r="P206" s="31"/>
+      <c r="Q206" s="31"/>
+      <c r="R206" s="31"/>
+      <c r="S206" s="31"/>
+      <c r="T206" s="31"/>
+      <c r="U206" s="32"/>
     </row>
     <row r="207" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="28"/>
@@ -16554,20 +16560,20 @@
       <c r="E207" s="29"/>
       <c r="F207" s="29"/>
       <c r="G207" s="29"/>
-      <c r="H207" s="42"/>
-      <c r="I207" s="50"/>
-      <c r="J207" s="50"/>
-      <c r="K207" s="50"/>
-      <c r="L207" s="50"/>
-      <c r="M207" s="50"/>
-      <c r="N207" s="50"/>
-      <c r="O207" s="50"/>
-      <c r="P207" s="50"/>
-      <c r="Q207" s="50"/>
-      <c r="R207" s="50"/>
-      <c r="S207" s="50"/>
-      <c r="T207" s="50"/>
-      <c r="U207" s="43"/>
+      <c r="H207" s="30"/>
+      <c r="I207" s="31"/>
+      <c r="J207" s="31"/>
+      <c r="K207" s="31"/>
+      <c r="L207" s="31"/>
+      <c r="M207" s="31"/>
+      <c r="N207" s="31"/>
+      <c r="O207" s="31"/>
+      <c r="P207" s="31"/>
+      <c r="Q207" s="31"/>
+      <c r="R207" s="31"/>
+      <c r="S207" s="31"/>
+      <c r="T207" s="31"/>
+      <c r="U207" s="32"/>
     </row>
     <row r="208" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A208" s="28"/>
@@ -16583,20 +16589,20 @@
       <c r="E208" s="29"/>
       <c r="F208" s="29"/>
       <c r="G208" s="29"/>
-      <c r="H208" s="42"/>
-      <c r="I208" s="50"/>
-      <c r="J208" s="50"/>
-      <c r="K208" s="50"/>
-      <c r="L208" s="50"/>
-      <c r="M208" s="50"/>
-      <c r="N208" s="50"/>
-      <c r="O208" s="50"/>
-      <c r="P208" s="50"/>
-      <c r="Q208" s="50"/>
-      <c r="R208" s="50"/>
-      <c r="S208" s="50"/>
-      <c r="T208" s="50"/>
-      <c r="U208" s="43"/>
+      <c r="H208" s="30"/>
+      <c r="I208" s="31"/>
+      <c r="J208" s="31"/>
+      <c r="K208" s="31"/>
+      <c r="L208" s="31"/>
+      <c r="M208" s="31"/>
+      <c r="N208" s="31"/>
+      <c r="O208" s="31"/>
+      <c r="P208" s="31"/>
+      <c r="Q208" s="31"/>
+      <c r="R208" s="31"/>
+      <c r="S208" s="31"/>
+      <c r="T208" s="31"/>
+      <c r="U208" s="32"/>
     </row>
     <row r="209" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="28"/>
@@ -16612,20 +16618,20 @@
       <c r="E209" s="29"/>
       <c r="F209" s="29"/>
       <c r="G209" s="29"/>
-      <c r="H209" s="42"/>
-      <c r="I209" s="50"/>
-      <c r="J209" s="50"/>
-      <c r="K209" s="50"/>
-      <c r="L209" s="50"/>
-      <c r="M209" s="50"/>
-      <c r="N209" s="50"/>
-      <c r="O209" s="50"/>
-      <c r="P209" s="50"/>
-      <c r="Q209" s="50"/>
-      <c r="R209" s="50"/>
-      <c r="S209" s="50"/>
-      <c r="T209" s="50"/>
-      <c r="U209" s="43"/>
+      <c r="H209" s="30"/>
+      <c r="I209" s="31"/>
+      <c r="J209" s="31"/>
+      <c r="K209" s="31"/>
+      <c r="L209" s="31"/>
+      <c r="M209" s="31"/>
+      <c r="N209" s="31"/>
+      <c r="O209" s="31"/>
+      <c r="P209" s="31"/>
+      <c r="Q209" s="31"/>
+      <c r="R209" s="31"/>
+      <c r="S209" s="31"/>
+      <c r="T209" s="31"/>
+      <c r="U209" s="32"/>
     </row>
     <row r="210" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="28"/>
@@ -16641,20 +16647,20 @@
       <c r="E210" s="29"/>
       <c r="F210" s="29"/>
       <c r="G210" s="29"/>
-      <c r="H210" s="42"/>
-      <c r="I210" s="50"/>
-      <c r="J210" s="50"/>
-      <c r="K210" s="50"/>
-      <c r="L210" s="50"/>
-      <c r="M210" s="50"/>
-      <c r="N210" s="50"/>
-      <c r="O210" s="50"/>
-      <c r="P210" s="50"/>
-      <c r="Q210" s="50"/>
-      <c r="R210" s="50"/>
-      <c r="S210" s="50"/>
-      <c r="T210" s="50"/>
-      <c r="U210" s="43"/>
+      <c r="H210" s="30"/>
+      <c r="I210" s="31"/>
+      <c r="J210" s="31"/>
+      <c r="K210" s="31"/>
+      <c r="L210" s="31"/>
+      <c r="M210" s="31"/>
+      <c r="N210" s="31"/>
+      <c r="O210" s="31"/>
+      <c r="P210" s="31"/>
+      <c r="Q210" s="31"/>
+      <c r="R210" s="31"/>
+      <c r="S210" s="31"/>
+      <c r="T210" s="31"/>
+      <c r="U210" s="32"/>
     </row>
     <row r="211" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A211" s="28"/>
@@ -16670,20 +16676,20 @@
       <c r="E211" s="29"/>
       <c r="F211" s="29"/>
       <c r="G211" s="29"/>
-      <c r="H211" s="42"/>
-      <c r="I211" s="50"/>
-      <c r="J211" s="50"/>
-      <c r="K211" s="50"/>
-      <c r="L211" s="50"/>
-      <c r="M211" s="50"/>
-      <c r="N211" s="50"/>
-      <c r="O211" s="50"/>
-      <c r="P211" s="50"/>
-      <c r="Q211" s="50"/>
-      <c r="R211" s="50"/>
-      <c r="S211" s="50"/>
-      <c r="T211" s="50"/>
-      <c r="U211" s="43"/>
+      <c r="H211" s="30"/>
+      <c r="I211" s="31"/>
+      <c r="J211" s="31"/>
+      <c r="K211" s="31"/>
+      <c r="L211" s="31"/>
+      <c r="M211" s="31"/>
+      <c r="N211" s="31"/>
+      <c r="O211" s="31"/>
+      <c r="P211" s="31"/>
+      <c r="Q211" s="31"/>
+      <c r="R211" s="31"/>
+      <c r="S211" s="31"/>
+      <c r="T211" s="31"/>
+      <c r="U211" s="32"/>
     </row>
     <row r="212" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A212" s="28"/>
@@ -16699,20 +16705,20 @@
       <c r="E212" s="29"/>
       <c r="F212" s="29"/>
       <c r="G212" s="29"/>
-      <c r="H212" s="42"/>
-      <c r="I212" s="50"/>
-      <c r="J212" s="50"/>
-      <c r="K212" s="50"/>
-      <c r="L212" s="50"/>
-      <c r="M212" s="50"/>
-      <c r="N212" s="50"/>
-      <c r="O212" s="50"/>
-      <c r="P212" s="50"/>
-      <c r="Q212" s="50"/>
-      <c r="R212" s="50"/>
-      <c r="S212" s="50"/>
-      <c r="T212" s="50"/>
-      <c r="U212" s="43"/>
+      <c r="H212" s="30"/>
+      <c r="I212" s="31"/>
+      <c r="J212" s="31"/>
+      <c r="K212" s="31"/>
+      <c r="L212" s="31"/>
+      <c r="M212" s="31"/>
+      <c r="N212" s="31"/>
+      <c r="O212" s="31"/>
+      <c r="P212" s="31"/>
+      <c r="Q212" s="31"/>
+      <c r="R212" s="31"/>
+      <c r="S212" s="31"/>
+      <c r="T212" s="31"/>
+      <c r="U212" s="32"/>
     </row>
     <row r="213" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="28"/>
@@ -16728,20 +16734,20 @@
       <c r="E213" s="29"/>
       <c r="F213" s="29"/>
       <c r="G213" s="29"/>
-      <c r="H213" s="42"/>
-      <c r="I213" s="50"/>
-      <c r="J213" s="50"/>
-      <c r="K213" s="50"/>
-      <c r="L213" s="50"/>
-      <c r="M213" s="50"/>
-      <c r="N213" s="50"/>
-      <c r="O213" s="50"/>
-      <c r="P213" s="50"/>
-      <c r="Q213" s="50"/>
-      <c r="R213" s="50"/>
-      <c r="S213" s="50"/>
-      <c r="T213" s="50"/>
-      <c r="U213" s="43"/>
+      <c r="H213" s="30"/>
+      <c r="I213" s="31"/>
+      <c r="J213" s="31"/>
+      <c r="K213" s="31"/>
+      <c r="L213" s="31"/>
+      <c r="M213" s="31"/>
+      <c r="N213" s="31"/>
+      <c r="O213" s="31"/>
+      <c r="P213" s="31"/>
+      <c r="Q213" s="31"/>
+      <c r="R213" s="31"/>
+      <c r="S213" s="31"/>
+      <c r="T213" s="31"/>
+      <c r="U213" s="32"/>
     </row>
     <row r="214" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="28"/>
@@ -16757,20 +16763,20 @@
       <c r="E214" s="29"/>
       <c r="F214" s="29"/>
       <c r="G214" s="29"/>
-      <c r="H214" s="42"/>
-      <c r="I214" s="50"/>
-      <c r="J214" s="50"/>
-      <c r="K214" s="50"/>
-      <c r="L214" s="50"/>
-      <c r="M214" s="50"/>
-      <c r="N214" s="50"/>
-      <c r="O214" s="50"/>
-      <c r="P214" s="50"/>
-      <c r="Q214" s="50"/>
-      <c r="R214" s="50"/>
-      <c r="S214" s="50"/>
-      <c r="T214" s="50"/>
-      <c r="U214" s="43"/>
+      <c r="H214" s="30"/>
+      <c r="I214" s="31"/>
+      <c r="J214" s="31"/>
+      <c r="K214" s="31"/>
+      <c r="L214" s="31"/>
+      <c r="M214" s="31"/>
+      <c r="N214" s="31"/>
+      <c r="O214" s="31"/>
+      <c r="P214" s="31"/>
+      <c r="Q214" s="31"/>
+      <c r="R214" s="31"/>
+      <c r="S214" s="31"/>
+      <c r="T214" s="31"/>
+      <c r="U214" s="32"/>
     </row>
     <row r="215" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A215" s="28"/>
@@ -16786,20 +16792,20 @@
       <c r="E215" s="29"/>
       <c r="F215" s="29"/>
       <c r="G215" s="29"/>
-      <c r="H215" s="42"/>
-      <c r="I215" s="50"/>
-      <c r="J215" s="50"/>
-      <c r="K215" s="50"/>
-      <c r="L215" s="50"/>
-      <c r="M215" s="50"/>
-      <c r="N215" s="50"/>
-      <c r="O215" s="50"/>
-      <c r="P215" s="50"/>
-      <c r="Q215" s="50"/>
-      <c r="R215" s="50"/>
-      <c r="S215" s="50"/>
-      <c r="T215" s="50"/>
-      <c r="U215" s="43"/>
+      <c r="H215" s="30"/>
+      <c r="I215" s="31"/>
+      <c r="J215" s="31"/>
+      <c r="K215" s="31"/>
+      <c r="L215" s="31"/>
+      <c r="M215" s="31"/>
+      <c r="N215" s="31"/>
+      <c r="O215" s="31"/>
+      <c r="P215" s="31"/>
+      <c r="Q215" s="31"/>
+      <c r="R215" s="31"/>
+      <c r="S215" s="31"/>
+      <c r="T215" s="31"/>
+      <c r="U215" s="32"/>
     </row>
     <row r="216" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A216" s="28"/>
@@ -16815,20 +16821,20 @@
       <c r="E216" s="29"/>
       <c r="F216" s="29"/>
       <c r="G216" s="29"/>
-      <c r="H216" s="42"/>
-      <c r="I216" s="50"/>
-      <c r="J216" s="50"/>
-      <c r="K216" s="50"/>
-      <c r="L216" s="50"/>
-      <c r="M216" s="50"/>
-      <c r="N216" s="50"/>
-      <c r="O216" s="50"/>
-      <c r="P216" s="50"/>
-      <c r="Q216" s="50"/>
-      <c r="R216" s="50"/>
-      <c r="S216" s="50"/>
-      <c r="T216" s="50"/>
-      <c r="U216" s="43"/>
+      <c r="H216" s="30"/>
+      <c r="I216" s="31"/>
+      <c r="J216" s="31"/>
+      <c r="K216" s="31"/>
+      <c r="L216" s="31"/>
+      <c r="M216" s="31"/>
+      <c r="N216" s="31"/>
+      <c r="O216" s="31"/>
+      <c r="P216" s="31"/>
+      <c r="Q216" s="31"/>
+      <c r="R216" s="31"/>
+      <c r="S216" s="31"/>
+      <c r="T216" s="31"/>
+      <c r="U216" s="32"/>
     </row>
     <row r="217" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A217" s="28"/>
@@ -16844,20 +16850,20 @@
       <c r="E217" s="29"/>
       <c r="F217" s="29"/>
       <c r="G217" s="29"/>
-      <c r="H217" s="42"/>
-      <c r="I217" s="50"/>
-      <c r="J217" s="50"/>
-      <c r="K217" s="50"/>
-      <c r="L217" s="50"/>
-      <c r="M217" s="50"/>
-      <c r="N217" s="50"/>
-      <c r="O217" s="50"/>
-      <c r="P217" s="50"/>
-      <c r="Q217" s="50"/>
-      <c r="R217" s="50"/>
-      <c r="S217" s="50"/>
-      <c r="T217" s="50"/>
-      <c r="U217" s="43"/>
+      <c r="H217" s="30"/>
+      <c r="I217" s="31"/>
+      <c r="J217" s="31"/>
+      <c r="K217" s="31"/>
+      <c r="L217" s="31"/>
+      <c r="M217" s="31"/>
+      <c r="N217" s="31"/>
+      <c r="O217" s="31"/>
+      <c r="P217" s="31"/>
+      <c r="Q217" s="31"/>
+      <c r="R217" s="31"/>
+      <c r="S217" s="31"/>
+      <c r="T217" s="31"/>
+      <c r="U217" s="32"/>
     </row>
     <row r="218" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="28"/>
@@ -16873,20 +16879,20 @@
       <c r="E218" s="29"/>
       <c r="F218" s="29"/>
       <c r="G218" s="29"/>
-      <c r="H218" s="42"/>
-      <c r="I218" s="50"/>
-      <c r="J218" s="50"/>
-      <c r="K218" s="50"/>
-      <c r="L218" s="50"/>
-      <c r="M218" s="50"/>
-      <c r="N218" s="50"/>
-      <c r="O218" s="50"/>
-      <c r="P218" s="50"/>
-      <c r="Q218" s="50"/>
-      <c r="R218" s="50"/>
-      <c r="S218" s="50"/>
-      <c r="T218" s="50"/>
-      <c r="U218" s="43"/>
+      <c r="H218" s="30"/>
+      <c r="I218" s="31"/>
+      <c r="J218" s="31"/>
+      <c r="K218" s="31"/>
+      <c r="L218" s="31"/>
+      <c r="M218" s="31"/>
+      <c r="N218" s="31"/>
+      <c r="O218" s="31"/>
+      <c r="P218" s="31"/>
+      <c r="Q218" s="31"/>
+      <c r="R218" s="31"/>
+      <c r="S218" s="31"/>
+      <c r="T218" s="31"/>
+      <c r="U218" s="32"/>
     </row>
     <row r="219" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="28"/>
@@ -16902,22 +16908,22 @@
       <c r="E219" s="29"/>
       <c r="F219" s="29"/>
       <c r="G219" s="29"/>
-      <c r="H219" s="42" t="s">
+      <c r="H219" s="30" t="s">
         <v>796</v>
       </c>
-      <c r="I219" s="50"/>
-      <c r="J219" s="50"/>
-      <c r="K219" s="50"/>
-      <c r="L219" s="50"/>
-      <c r="M219" s="50"/>
-      <c r="N219" s="50"/>
-      <c r="O219" s="50"/>
-      <c r="P219" s="50"/>
-      <c r="Q219" s="50"/>
-      <c r="R219" s="50"/>
-      <c r="S219" s="50"/>
-      <c r="T219" s="50"/>
-      <c r="U219" s="43"/>
+      <c r="I219" s="31"/>
+      <c r="J219" s="31"/>
+      <c r="K219" s="31"/>
+      <c r="L219" s="31"/>
+      <c r="M219" s="31"/>
+      <c r="N219" s="31"/>
+      <c r="O219" s="31"/>
+      <c r="P219" s="31"/>
+      <c r="Q219" s="31"/>
+      <c r="R219" s="31"/>
+      <c r="S219" s="31"/>
+      <c r="T219" s="31"/>
+      <c r="U219" s="32"/>
     </row>
     <row r="220" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="28"/>
@@ -16933,20 +16939,20 @@
       <c r="E220" s="29"/>
       <c r="F220" s="29"/>
       <c r="G220" s="29"/>
-      <c r="H220" s="42"/>
-      <c r="I220" s="50"/>
-      <c r="J220" s="50"/>
-      <c r="K220" s="50"/>
-      <c r="L220" s="50"/>
-      <c r="M220" s="50"/>
-      <c r="N220" s="50"/>
-      <c r="O220" s="50"/>
-      <c r="P220" s="50"/>
-      <c r="Q220" s="50"/>
-      <c r="R220" s="50"/>
-      <c r="S220" s="50"/>
-      <c r="T220" s="50"/>
-      <c r="U220" s="43"/>
+      <c r="H220" s="30"/>
+      <c r="I220" s="31"/>
+      <c r="J220" s="31"/>
+      <c r="K220" s="31"/>
+      <c r="L220" s="31"/>
+      <c r="M220" s="31"/>
+      <c r="N220" s="31"/>
+      <c r="O220" s="31"/>
+      <c r="P220" s="31"/>
+      <c r="Q220" s="31"/>
+      <c r="R220" s="31"/>
+      <c r="S220" s="31"/>
+      <c r="T220" s="31"/>
+      <c r="U220" s="32"/>
     </row>
     <row r="221" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A221" s="28"/>
@@ -16960,20 +16966,20 @@
       <c r="E221" s="29"/>
       <c r="F221" s="29"/>
       <c r="G221" s="29"/>
-      <c r="H221" s="42"/>
-      <c r="I221" s="50"/>
-      <c r="J221" s="50"/>
-      <c r="K221" s="50"/>
-      <c r="L221" s="50"/>
-      <c r="M221" s="50"/>
-      <c r="N221" s="50"/>
-      <c r="O221" s="50"/>
-      <c r="P221" s="50"/>
-      <c r="Q221" s="50"/>
-      <c r="R221" s="50"/>
-      <c r="S221" s="50"/>
-      <c r="T221" s="50"/>
-      <c r="U221" s="43"/>
+      <c r="H221" s="30"/>
+      <c r="I221" s="31"/>
+      <c r="J221" s="31"/>
+      <c r="K221" s="31"/>
+      <c r="L221" s="31"/>
+      <c r="M221" s="31"/>
+      <c r="N221" s="31"/>
+      <c r="O221" s="31"/>
+      <c r="P221" s="31"/>
+      <c r="Q221" s="31"/>
+      <c r="R221" s="31"/>
+      <c r="S221" s="31"/>
+      <c r="T221" s="31"/>
+      <c r="U221" s="32"/>
     </row>
     <row r="222" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="28"/>
@@ -16987,20 +16993,20 @@
       <c r="E222" s="29"/>
       <c r="F222" s="29"/>
       <c r="G222" s="29"/>
-      <c r="H222" s="42"/>
-      <c r="I222" s="50"/>
-      <c r="J222" s="50"/>
-      <c r="K222" s="50"/>
-      <c r="L222" s="50"/>
-      <c r="M222" s="50"/>
-      <c r="N222" s="50"/>
-      <c r="O222" s="50"/>
-      <c r="P222" s="50"/>
-      <c r="Q222" s="50"/>
-      <c r="R222" s="50"/>
-      <c r="S222" s="50"/>
-      <c r="T222" s="50"/>
-      <c r="U222" s="43"/>
+      <c r="H222" s="30"/>
+      <c r="I222" s="31"/>
+      <c r="J222" s="31"/>
+      <c r="K222" s="31"/>
+      <c r="L222" s="31"/>
+      <c r="M222" s="31"/>
+      <c r="N222" s="31"/>
+      <c r="O222" s="31"/>
+      <c r="P222" s="31"/>
+      <c r="Q222" s="31"/>
+      <c r="R222" s="31"/>
+      <c r="S222" s="31"/>
+      <c r="T222" s="31"/>
+      <c r="U222" s="32"/>
     </row>
     <row r="223" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="28"/>
@@ -17014,72 +17020,25 @@
       <c r="E223" s="29"/>
       <c r="F223" s="29"/>
       <c r="G223" s="29"/>
-      <c r="H223" s="42"/>
-      <c r="I223" s="50"/>
-      <c r="J223" s="50"/>
-      <c r="K223" s="50"/>
-      <c r="L223" s="50"/>
-      <c r="M223" s="50"/>
-      <c r="N223" s="50"/>
-      <c r="O223" s="50"/>
-      <c r="P223" s="50"/>
-      <c r="Q223" s="50"/>
-      <c r="R223" s="50"/>
-      <c r="S223" s="50"/>
-      <c r="T223" s="50"/>
-      <c r="U223" s="43"/>
+      <c r="H223" s="30"/>
+      <c r="I223" s="31"/>
+      <c r="J223" s="31"/>
+      <c r="K223" s="31"/>
+      <c r="L223" s="31"/>
+      <c r="M223" s="31"/>
+      <c r="N223" s="31"/>
+      <c r="O223" s="31"/>
+      <c r="P223" s="31"/>
+      <c r="Q223" s="31"/>
+      <c r="R223" s="31"/>
+      <c r="S223" s="31"/>
+      <c r="T223" s="31"/>
+      <c r="U223" s="32"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="63">
-    <mergeCell ref="H222:U222"/>
-    <mergeCell ref="H223:U223"/>
-    <mergeCell ref="H217:U217"/>
-    <mergeCell ref="H218:U218"/>
-    <mergeCell ref="H219:U219"/>
-    <mergeCell ref="H220:U220"/>
-    <mergeCell ref="H221:U221"/>
-    <mergeCell ref="H212:U212"/>
-    <mergeCell ref="H213:U213"/>
-    <mergeCell ref="H214:U214"/>
-    <mergeCell ref="H215:U215"/>
-    <mergeCell ref="H216:U216"/>
-    <mergeCell ref="H207:U207"/>
-    <mergeCell ref="H208:U208"/>
-    <mergeCell ref="H209:U209"/>
-    <mergeCell ref="H210:U210"/>
-    <mergeCell ref="H211:U211"/>
-    <mergeCell ref="C172:I172"/>
-    <mergeCell ref="C194:I194"/>
-    <mergeCell ref="C201:I201"/>
-    <mergeCell ref="A205:U205"/>
-    <mergeCell ref="H206:U206"/>
-    <mergeCell ref="C59:I59"/>
-    <mergeCell ref="C92:I92"/>
-    <mergeCell ref="C93:I93"/>
-    <mergeCell ref="C167:I167"/>
-    <mergeCell ref="C171:I171"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C50:I50"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -17096,6 +17055,53 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="C59:I59"/>
+    <mergeCell ref="C92:I92"/>
+    <mergeCell ref="C93:I93"/>
+    <mergeCell ref="C167:I167"/>
+    <mergeCell ref="C171:I171"/>
+    <mergeCell ref="C172:I172"/>
+    <mergeCell ref="C194:I194"/>
+    <mergeCell ref="C201:I201"/>
+    <mergeCell ref="A205:U205"/>
+    <mergeCell ref="H206:U206"/>
+    <mergeCell ref="H207:U207"/>
+    <mergeCell ref="H208:U208"/>
+    <mergeCell ref="H209:U209"/>
+    <mergeCell ref="H210:U210"/>
+    <mergeCell ref="H211:U211"/>
+    <mergeCell ref="H212:U212"/>
+    <mergeCell ref="H213:U213"/>
+    <mergeCell ref="H214:U214"/>
+    <mergeCell ref="H215:U215"/>
+    <mergeCell ref="H216:U216"/>
+    <mergeCell ref="H222:U222"/>
+    <mergeCell ref="H223:U223"/>
+    <mergeCell ref="H217:U217"/>
+    <mergeCell ref="H218:U218"/>
+    <mergeCell ref="H219:U219"/>
+    <mergeCell ref="H220:U220"/>
+    <mergeCell ref="H221:U221"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="28" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
